--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF405"/>
+  <dimension ref="A1:AH405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,16 @@
       <c r="AF1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -675,6 +685,16 @@
           <t>010102</t>
         </is>
       </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -773,6 +793,16 @@
           <t>010102</t>
         </is>
       </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -871,6 +901,16 @@
           <t>010103</t>
         </is>
       </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -969,6 +1009,16 @@
           <t>010103</t>
         </is>
       </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1067,6 +1117,16 @@
           <t>010103</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1165,6 +1225,16 @@
           <t>010103</t>
         </is>
       </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1263,6 +1333,16 @@
           <t>010103</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1401,6 +1481,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1635,16 @@
       <c r="AF10" t="inlineStr">
         <is>
           <t>010101</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1745,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1909,16 @@
       <c r="AF12" t="inlineStr">
         <is>
           <t>010101</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
     </row>
@@ -1943,6 +2063,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2219,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2375,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2531,16 @@
           <t>010604</t>
         </is>
       </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>UGEL RODRÍGUEZ DE MENDOZA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2527,6 +2687,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2671,6 +2841,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2815,6 +2995,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -2959,6 +3149,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -3103,6 +3303,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -3247,6 +3457,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -3391,6 +3611,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -3535,6 +3765,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3681,6 +3921,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -3825,6 +4075,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -3969,6 +4229,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -4113,6 +4383,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4259,6 +4539,16 @@
           <t>010111</t>
         </is>
       </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4395,6 +4685,16 @@
       <c r="AF30" t="inlineStr">
         <is>
           <t>010515</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
         </is>
       </c>
     </row>
@@ -4539,6 +4839,16 @@
           <t>010520</t>
         </is>
       </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4685,6 +4995,16 @@
           <t>021001</t>
         </is>
       </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4831,6 +5151,16 @@
           <t>021001</t>
         </is>
       </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4975,6 +5305,16 @@
       <c r="AF34" t="inlineStr">
         <is>
           <t>021001</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
         </is>
       </c>
     </row>
@@ -5097,6 +5437,8 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5199,6 +5541,16 @@
           <t>022003</t>
         </is>
       </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5341,6 +5693,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5475,6 +5837,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5617,6 +5989,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5759,6 +6141,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5901,6 +6293,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6043,6 +6445,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6185,6 +6597,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6331,6 +6753,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6477,6 +6909,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6621,6 +7063,16 @@
       <c r="AF46" t="inlineStr">
         <is>
           <t>022001</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
     </row>
@@ -6725,6 +7177,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6871,6 +7333,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7017,6 +7489,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -7159,6 +7641,16 @@
       <c r="AF50" t="inlineStr">
         <is>
           <t>022001</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
         </is>
       </c>
     </row>
@@ -7263,6 +7755,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7409,6 +7911,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7555,6 +8067,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7701,6 +8223,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7847,6 +8379,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7993,6 +8535,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8139,6 +8691,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8285,6 +8847,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8431,6 +9003,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8577,6 +9159,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8723,6 +9315,16 @@
           <t>030202</t>
         </is>
       </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8867,6 +9469,16 @@
       <c r="AF62" t="inlineStr">
         <is>
           <t>030202</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
     </row>
@@ -9001,6 +9613,16 @@
           <t>030219</t>
         </is>
       </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9147,6 +9769,16 @@
           <t>030219</t>
         </is>
       </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9291,6 +9923,16 @@
       <c r="AF65" t="inlineStr">
         <is>
           <t>030219</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
     </row>
@@ -9393,6 +10035,16 @@
           <t>030219</t>
         </is>
       </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9539,6 +10191,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9685,6 +10347,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9829,6 +10501,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9973,6 +10655,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10117,6 +10809,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10261,6 +10963,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10405,6 +11117,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10549,6 +11271,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10695,6 +11427,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10839,6 +11581,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10977,6 +11729,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11115,6 +11877,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11253,6 +12025,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11391,6 +12173,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11529,6 +12321,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11667,6 +12469,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11805,6 +12617,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11941,6 +12763,16 @@
       <c r="AF84" t="inlineStr">
         <is>
           <t>040205</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
         </is>
       </c>
     </row>
@@ -12041,6 +12873,16 @@
           <t>040409</t>
         </is>
       </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>UGEL CASTILLA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12137,6 +12979,16 @@
       <c r="AF86" t="inlineStr">
         <is>
           <t>040409</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>UGEL CASTILLA</t>
         </is>
       </c>
     </row>
@@ -12233,6 +13085,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12327,6 +13189,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12419,6 +13291,16 @@
       <c r="AF89" t="inlineStr">
         <is>
           <t>040117</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
     </row>
@@ -12513,6 +13395,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12605,6 +13497,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12697,6 +13599,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12791,6 +13703,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12885,6 +13807,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12979,6 +13911,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13073,6 +14015,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13165,6 +14117,16 @@
       <c r="AF97" t="inlineStr">
         <is>
           <t>040117</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
     </row>
@@ -13259,6 +14221,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13405,6 +14377,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13551,6 +14533,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13697,6 +14689,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13843,6 +14845,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13989,6 +15001,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14133,6 +15155,16 @@
       <c r="AF104" t="inlineStr">
         <is>
           <t>040124</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
     </row>
@@ -14277,6 +15309,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -14417,6 +15459,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14559,6 +15611,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -14699,6 +15761,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14841,6 +15913,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -14983,6 +16065,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -15123,6 +16215,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15265,6 +16367,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15407,6 +16519,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15553,6 +16675,16 @@
           <t>060402</t>
         </is>
       </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15699,6 +16831,16 @@
           <t>060408</t>
         </is>
       </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15835,6 +16977,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15971,6 +17123,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16107,6 +17269,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16243,6 +17415,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16379,6 +17561,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16515,6 +17707,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16661,6 +17863,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16807,6 +18019,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16953,6 +18175,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17099,6 +18331,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17245,6 +18487,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17391,6 +18643,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17537,6 +18799,16 @@
           <t>060410</t>
         </is>
       </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17689,6 +18961,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17829,6 +19111,16 @@
       <c r="AF130" t="inlineStr">
         <is>
           <t>070107</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
     </row>
@@ -17919,6 +19211,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18065,6 +19367,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18219,6 +19531,16 @@
       <c r="AF133" t="inlineStr">
         <is>
           <t>070107</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
     </row>
@@ -18353,6 +19675,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18489,6 +19821,16 @@
       <c r="AF135" t="inlineStr">
         <is>
           <t>070107</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
     </row>
@@ -18623,6 +19965,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18765,6 +20117,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18911,6 +20273,16 @@
           <t>081003</t>
         </is>
       </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>UGEL PARURO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -19067,6 +20439,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19223,6 +20605,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19363,6 +20755,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19519,6 +20921,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -19675,6 +21087,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -19821,6 +21243,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19977,6 +21409,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -20123,6 +21565,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -20279,6 +21731,16 @@
           <t>080914</t>
         </is>
       </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -20425,6 +21887,16 @@
           <t>080805</t>
         </is>
       </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -20577,6 +22049,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -20729,6 +22211,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -20881,6 +22373,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -21025,6 +22527,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -21169,6 +22681,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -21313,6 +22835,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -21465,6 +22997,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -21617,6 +23159,16 @@
           <t>080910</t>
         </is>
       </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -21759,6 +23311,16 @@
       <c r="AF157" t="inlineStr">
         <is>
           <t>080910</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
     </row>
@@ -21895,6 +23457,16 @@
           <t>081212</t>
         </is>
       </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -22041,6 +23613,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -22185,6 +23767,16 @@
       <c r="AF160" t="inlineStr">
         <is>
           <t>090309</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
     </row>
@@ -22321,6 +23913,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -22467,6 +24069,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -22613,6 +24225,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -22759,6 +24381,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -22915,6 +24547,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -23061,6 +24703,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -23207,6 +24859,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -23363,6 +25025,16 @@
           <t>101006</t>
         </is>
       </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -23509,6 +25181,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -23655,6 +25337,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -23801,6 +25493,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -23947,6 +25649,16 @@
           <t>110501</t>
         </is>
       </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -24093,6 +25805,16 @@
           <t>110501</t>
         </is>
       </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -24239,6 +25961,16 @@
           <t>110501</t>
         </is>
       </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -24385,6 +26117,16 @@
           <t>110501</t>
         </is>
       </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -24519,6 +26261,16 @@
           <t>110107</t>
         </is>
       </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -24675,6 +26427,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -24831,6 +26593,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -24987,6 +26759,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -25143,6 +26925,16 @@
           <t>120603</t>
         </is>
       </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -25297,6 +27089,16 @@
       <c r="AF181" t="inlineStr">
         <is>
           <t>120603</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
         </is>
       </c>
     </row>
@@ -25401,6 +27203,16 @@
           <t>120433</t>
         </is>
       </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -25503,6 +27315,16 @@
           <t>120433</t>
         </is>
       </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -25605,6 +27427,16 @@
           <t>120433</t>
         </is>
       </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -25761,6 +27593,16 @@
           <t>130804</t>
         </is>
       </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -25907,6 +27749,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -26053,6 +27905,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -26195,6 +28057,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -26341,6 +28213,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -26487,6 +28369,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -26633,6 +28525,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -26779,6 +28681,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -26925,6 +28837,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -27071,6 +28993,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -27215,6 +29147,16 @@
       <c r="AF195" t="inlineStr">
         <is>
           <t>150132</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
     </row>
@@ -27315,6 +29257,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -27413,6 +29365,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -27511,6 +29473,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -27601,6 +29573,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -27699,6 +29681,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -27797,6 +29789,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -27895,6 +29897,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -27993,6 +30005,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -28091,6 +30113,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -28189,6 +30221,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -28287,6 +30329,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -28385,6 +30437,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -28483,6 +30545,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -28581,6 +30653,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -28727,6 +30809,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -28871,6 +30963,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -29017,6 +31119,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -29163,6 +31275,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -29307,6 +31429,16 @@
       <c r="AF214" t="inlineStr">
         <is>
           <t>150812</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
         </is>
       </c>
     </row>
@@ -29417,6 +31549,16 @@
           <t>160801</t>
         </is>
       </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>UGEL PUTUMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -29527,6 +31669,16 @@
           <t>160801</t>
         </is>
       </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>UGEL PUTUMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -29683,6 +31835,16 @@
           <t>160507</t>
         </is>
       </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -29839,6 +32001,16 @@
           <t>160507</t>
         </is>
       </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -29995,6 +32167,16 @@
           <t>160507</t>
         </is>
       </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -30149,6 +32331,16 @@
       <c r="AF220" t="inlineStr">
         <is>
           <t>170202</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
         </is>
       </c>
     </row>
@@ -30279,6 +32471,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -30435,6 +32637,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -30591,6 +32803,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -30747,6 +32969,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -30903,6 +33135,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -31059,6 +33301,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -31215,6 +33467,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -31371,6 +33633,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -31527,6 +33799,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -31683,6 +33965,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -31839,6 +34131,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -31979,6 +34281,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -32133,6 +34445,16 @@
       <c r="AF233" t="inlineStr">
         <is>
           <t>170204</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
         </is>
       </c>
     </row>
@@ -32263,6 +34585,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -32419,6 +34751,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -32575,6 +34917,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -32731,6 +35083,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -32885,6 +35247,16 @@
       <c r="AF238" t="inlineStr">
         <is>
           <t>170302</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -33015,6 +35387,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -33171,6 +35553,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -33327,6 +35719,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -33467,6 +35869,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -33623,6 +36035,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -33777,6 +36199,16 @@
       <c r="AF244" t="inlineStr">
         <is>
           <t>170102</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -33907,6 +36339,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -34035,6 +36477,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -34163,6 +36615,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -34317,6 +36779,16 @@
       <c r="AF248" t="inlineStr">
         <is>
           <t>170102</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -34447,6 +36919,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -34601,6 +37083,16 @@
       <c r="AF250" t="inlineStr">
         <is>
           <t>170102</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -34731,6 +37223,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -34859,6 +37361,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -35015,6 +37527,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -35171,6 +37693,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -35325,6 +37857,16 @@
       <c r="AF255" t="inlineStr">
         <is>
           <t>170102</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -35455,6 +37997,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -35611,6 +38163,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -35749,6 +38311,16 @@
       <c r="AF258" t="inlineStr">
         <is>
           <t>170301</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -35879,6 +38451,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -36019,6 +38601,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -36173,6 +38765,16 @@
       <c r="AF261" t="inlineStr">
         <is>
           <t>170301</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -36303,6 +38905,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -36443,6 +39055,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -36581,6 +39203,16 @@
       <c r="AF264" t="inlineStr">
         <is>
           <t>170104</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -36711,6 +39343,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -36849,6 +39491,16 @@
       <c r="AF266" t="inlineStr">
         <is>
           <t>170104</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -36979,6 +39631,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -37117,6 +39779,16 @@
       <c r="AF268" t="inlineStr">
         <is>
           <t>170104</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -37247,6 +39919,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -37387,6 +40069,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -37541,6 +40233,16 @@
       <c r="AF271" t="inlineStr">
         <is>
           <t>170104</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -37671,6 +40373,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -37825,6 +40537,16 @@
       <c r="AF273" t="inlineStr">
         <is>
           <t>170103</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -37955,6 +40677,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -38109,6 +40841,16 @@
       <c r="AF275" t="inlineStr">
         <is>
           <t>170103</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -38239,6 +40981,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -38395,6 +41147,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -38535,6 +41297,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -38691,6 +41463,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -38847,6 +41629,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -39003,6 +41795,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -39157,6 +41959,16 @@
       <c r="AF282" t="inlineStr">
         <is>
           <t>170103</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -39287,6 +42099,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -39415,6 +42237,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -39543,6 +42375,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -39699,6 +42541,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -39855,6 +42707,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -40011,6 +42873,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -40165,6 +43037,16 @@
       <c r="AF289" t="inlineStr">
         <is>
           <t>170203</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -40295,6 +43177,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -40449,6 +43341,16 @@
       <c r="AF291" t="inlineStr">
         <is>
           <t>170203</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
         </is>
       </c>
     </row>
@@ -40579,6 +43481,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -40707,6 +43619,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -40845,6 +43767,16 @@
       <c r="AF294" t="inlineStr">
         <is>
           <t>170203</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH294" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -40975,6 +43907,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -41103,6 +44045,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -41231,6 +44183,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -41385,6 +44347,16 @@
       <c r="AF298" t="inlineStr">
         <is>
           <t>170201</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
         </is>
       </c>
     </row>
@@ -41515,6 +44487,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -41643,6 +44625,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -41781,6 +44773,16 @@
       <c r="AF301" t="inlineStr">
         <is>
           <t>170201</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
         </is>
       </c>
     </row>
@@ -41911,6 +44913,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -42039,6 +45051,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -42167,6 +45189,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -42305,6 +45337,16 @@
       <c r="AF305" t="inlineStr">
         <is>
           <t>170303</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -42435,6 +45477,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -42563,6 +45615,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -42717,6 +45779,16 @@
       <c r="AF308" t="inlineStr">
         <is>
           <t>170303</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -42847,6 +45919,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -42985,6 +46067,16 @@
       <c r="AF310" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -43115,6 +46207,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -43243,6 +46345,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -43399,6 +46511,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -43553,6 +46675,16 @@
       <c r="AF314" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -43683,6 +46815,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -43839,6 +46981,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -43991,6 +47143,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -44143,6 +47305,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -44299,6 +47471,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -44437,6 +47619,16 @@
       <c r="AF320" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -44567,6 +47759,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -44695,6 +47897,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -44823,6 +48035,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -44963,6 +48185,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -45103,6 +48335,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -45257,6 +48499,16 @@
       <c r="AF326" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -45387,6 +48639,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -45543,6 +48805,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -45697,6 +48969,16 @@
       <c r="AF329" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -45827,6 +49109,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -45981,6 +49273,16 @@
       <c r="AF331" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -46111,6 +49413,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -46263,6 +49575,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -46415,6 +49737,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -46569,6 +49901,16 @@
       <c r="AF335" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -46699,6 +50041,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -46849,6 +50201,16 @@
       <c r="AF337" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -46979,6 +50341,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -47107,6 +50479,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -47261,6 +50643,16 @@
       <c r="AF340" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -47395,6 +50787,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -47527,6 +50929,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -47673,6 +51085,16 @@
           <t>180302</t>
         </is>
       </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -47819,6 +51241,16 @@
           <t>180302</t>
         </is>
       </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -47963,6 +51395,16 @@
       <c r="AF345" t="inlineStr">
         <is>
           <t>190111</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
         </is>
       </c>
     </row>
@@ -48099,6 +51541,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -48233,6 +51685,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -48367,6 +51829,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -48513,6 +51985,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -48659,6 +52141,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -48805,6 +52297,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -48951,6 +52453,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -49097,6 +52609,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -49241,6 +52763,16 @@
       <c r="AF354" t="inlineStr">
         <is>
           <t>190111</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
         </is>
       </c>
     </row>
@@ -49339,6 +52871,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -49437,6 +52979,16 @@
       <c r="AF356" t="inlineStr">
         <is>
           <t>200104</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
         </is>
       </c>
     </row>
@@ -49535,6 +53087,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -49631,6 +53193,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -49727,6 +53299,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -49823,6 +53405,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -49919,6 +53511,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -50019,6 +53621,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -50157,6 +53769,16 @@
           <t>220808</t>
         </is>
       </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -50287,6 +53909,16 @@
       <c r="AF364" t="inlineStr">
         <is>
           <t>230104</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -50429,6 +54061,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -50577,6 +54219,16 @@
           <t>230105</t>
         </is>
       </c>
+      <c r="AG366" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -50725,6 +54377,16 @@
           <t>230105</t>
         </is>
       </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -50871,6 +54533,16 @@
       <c r="AF368" t="inlineStr">
         <is>
           <t>230105</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -51011,6 +54683,16 @@
           <t>230105</t>
         </is>
       </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -51157,6 +54839,16 @@
       <c r="AF370" t="inlineStr">
         <is>
           <t>230105</t>
+        </is>
+      </c>
+      <c r="AG370" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH370" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -51297,6 +54989,16 @@
           <t>230105</t>
         </is>
       </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -51441,6 +55143,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -51585,6 +55297,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -51729,6 +55451,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -51873,6 +55605,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -52029,6 +55771,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -52175,6 +55927,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -52321,6 +56083,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -52467,6 +56239,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -52611,6 +56393,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -52757,6 +56549,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -52901,6 +56703,16 @@
       <c r="AF382" t="inlineStr">
         <is>
           <t>230109</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -53005,6 +56817,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -53149,6 +56971,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="AG384" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH384" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -53289,6 +57121,16 @@
       <c r="AF385" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -53433,6 +57275,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -53575,6 +57427,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="AG387" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -53707,6 +57569,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="AG388" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH388" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -53847,6 +57719,16 @@
       <c r="AF389" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -53989,6 +57871,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG390" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH390" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -54129,6 +58021,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG391" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH391" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -54269,6 +58171,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG392" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH392" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -54409,6 +58321,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG393" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH393" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -54549,6 +58471,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -54689,6 +58621,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG395" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH395" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -54829,6 +58771,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -54969,6 +58921,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG397" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -55109,6 +59071,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG398" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -55249,6 +59221,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="AG399" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -55387,6 +59369,16 @@
       <c r="AF400" t="inlineStr">
         <is>
           <t>230401</t>
+        </is>
+      </c>
+      <c r="AG400" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AH400" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
         </is>
       </c>
     </row>
@@ -55497,6 +59489,16 @@
       <c r="AF401" t="inlineStr">
         <is>
           <t>250306</t>
+        </is>
+      </c>
+      <c r="AG401" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
         </is>
       </c>
     </row>
@@ -55601,6 +59603,16 @@
           <t>250306</t>
         </is>
       </c>
+      <c r="AG402" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -55757,6 +59769,16 @@
           <t>250202</t>
         </is>
       </c>
+      <c r="AG403" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH403" t="inlineStr">
+        <is>
+          <t>UGEL ATALAYA</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -55913,6 +59935,16 @@
           <t>250202</t>
         </is>
       </c>
+      <c r="AG404" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH404" t="inlineStr">
+        <is>
+          <t>UGEL ATALAYA</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -56067,6 +60099,16 @@
       <c r="AF405" t="inlineStr">
         <is>
           <t>250202</t>
+        </is>
+      </c>
+      <c r="AG405" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>UGEL ATALAYA</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH405"/>
+  <dimension ref="A1:AI405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,11 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -695,6 +700,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -803,6 +813,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -911,6 +926,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1019,6 +1039,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1127,6 +1152,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1235,6 +1265,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1343,6 +1378,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
     </row>
@@ -1755,6 +1805,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
     </row>
@@ -2073,6 +2133,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2229,6 +2294,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2385,6 +2455,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2541,6 +2616,11 @@
           <t>UGEL RODRÍGUEZ DE MENDOZA</t>
         </is>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Huambo</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2697,6 +2777,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2851,6 +2936,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -3005,6 +3095,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -3159,6 +3254,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -3313,6 +3413,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -3467,6 +3572,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -3621,6 +3731,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -3775,6 +3890,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3931,6 +4051,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -4085,6 +4210,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -4239,6 +4369,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -4393,6 +4528,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4549,6 +4689,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Levanto</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4695,6 +4840,11 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>UGEL LUYA</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Luya</t>
         </is>
       </c>
     </row>
@@ -4849,6 +4999,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Luya</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5005,6 +5160,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huari</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5161,6 +5321,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huari</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5315,6 +5480,11 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>UGEL HUARI</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huari</t>
         </is>
       </c>
     </row>
@@ -5439,6 +5609,11 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huari</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5551,6 +5726,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5703,6 +5883,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5847,6 +6032,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5999,6 +6189,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6151,6 +6346,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6303,6 +6503,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6455,6 +6660,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6607,6 +6817,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pamparomas</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6763,6 +6978,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6919,6 +7139,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7073,6 +7298,11 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>UGEL YUNGAY</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
     </row>
@@ -7187,6 +7417,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7343,6 +7578,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7499,6 +7739,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -7651,6 +7896,11 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>UGEL YUNGAY</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
     </row>
@@ -7765,6 +8015,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7921,6 +8176,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Yungay</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8077,6 +8337,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8233,6 +8498,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8389,6 +8659,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8545,6 +8820,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8701,6 +8981,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8857,6 +9142,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9013,6 +9303,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9169,6 +9464,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9325,6 +9625,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9479,6 +9784,11 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
     </row>
@@ -9623,6 +9933,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Kaquiabamba</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9779,6 +10094,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Kaquiabamba</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9933,6 +10253,11 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Kaquiabamba</t>
         </is>
       </c>
     </row>
@@ -10045,6 +10370,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Kaquiabamba</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10201,6 +10531,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10357,6 +10692,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10511,6 +10851,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10665,6 +11010,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10819,6 +11169,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10973,6 +11328,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11127,6 +11487,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11281,6 +11646,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11437,6 +11807,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11591,6 +11966,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cerro Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11739,6 +12119,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11887,6 +12272,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12035,6 +12425,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12183,6 +12578,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12331,6 +12731,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12479,6 +12884,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12627,6 +13037,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12773,6 +13188,11 @@
       <c r="AH84" t="inlineStr">
         <is>
           <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
     </row>
@@ -12883,6 +13303,11 @@
           <t>UGEL CASTILLA</t>
         </is>
       </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Orcopampa</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12989,6 +13414,11 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>UGEL CASTILLA</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Orcopampa</t>
         </is>
       </c>
     </row>
@@ -13095,6 +13525,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13199,6 +13634,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13301,6 +13741,11 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
     </row>
@@ -13405,6 +13850,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13507,6 +13957,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13609,6 +14064,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13713,6 +14173,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13817,6 +14282,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13921,6 +14391,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -14025,6 +14500,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -14127,6 +14607,11 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
     </row>
@@ -14231,6 +14716,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sachaca</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14387,6 +14877,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14543,6 +15038,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14699,6 +15199,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14855,6 +15360,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -15011,6 +15521,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15165,6 +15680,11 @@
       <c r="AH104" t="inlineStr">
         <is>
           <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
     </row>
@@ -15319,6 +15839,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -15469,6 +15994,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15621,6 +16151,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -15771,6 +16306,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15923,6 +16463,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16075,6 +16620,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -16225,6 +16775,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16377,6 +16932,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16529,6 +17089,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yura</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16685,6 +17250,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Anguia</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16841,6 +17411,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Conchan</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16987,6 +17562,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -17133,6 +17713,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17279,6 +17864,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17425,6 +18015,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17571,6 +18166,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17717,6 +18317,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Encañada</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17873,6 +18478,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -18029,6 +18639,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -18185,6 +18800,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -18341,6 +18961,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -18497,6 +19122,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -18653,6 +19283,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -18809,6 +19444,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Lajas</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -18971,6 +19611,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -19121,6 +19766,11 @@
       <c r="AH130" t="inlineStr">
         <is>
           <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
     </row>
@@ -19221,6 +19871,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -19377,6 +20032,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -19541,6 +20201,11 @@
       <c r="AH133" t="inlineStr">
         <is>
           <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
     </row>
@@ -19685,6 +20350,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -19831,6 +20501,11 @@
       <c r="AH135" t="inlineStr">
         <is>
           <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
     </row>
@@ -19975,6 +20650,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -20127,6 +20807,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -20283,6 +20968,11 @@
           <t>UGEL PARURO</t>
         </is>
       </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ccapi</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -20449,6 +21139,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -20615,6 +21310,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -20765,6 +21465,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -20931,6 +21636,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -21097,6 +21807,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -21253,6 +21968,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -21419,6 +22139,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -21575,6 +22300,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -21741,6 +22471,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Megantoni</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -21897,6 +22632,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pallpata</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -22059,6 +22799,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -22221,6 +22966,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -22383,6 +23133,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -22537,6 +23292,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -22691,6 +23451,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -22845,6 +23610,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -23007,6 +23777,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23169,6 +23944,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -23321,6 +24101,11 @@
       <c r="AH157" t="inlineStr">
         <is>
           <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
     </row>
@@ -23467,6 +24252,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Quiquijana</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -23623,6 +24413,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -23777,6 +24572,11 @@
       <c r="AH160" t="inlineStr">
         <is>
           <t>UGEL ANGARAES</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
     </row>
@@ -23923,6 +24723,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -24079,6 +24884,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -24235,6 +25045,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -24391,6 +25206,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -24557,6 +25377,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -24713,6 +25538,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -24869,6 +25699,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -25035,6 +25870,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Francisco de Asis</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -25191,6 +26031,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25347,6 +26192,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25503,6 +26353,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -25659,6 +26514,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Pisco</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -25815,6 +26675,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Pisco</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -25971,6 +26836,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Pisco</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -26127,6 +26997,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Pisco</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -26271,6 +27146,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pueblo Nuevo</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -26437,6 +27317,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -26603,6 +27488,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -26769,6 +27659,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -26935,6 +27830,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -27099,6 +27999,11 @@
       <c r="AH181" t="inlineStr">
         <is>
           <t>UGEL SATIPO</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
     </row>
@@ -27213,6 +28118,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauli</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -27325,6 +28235,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauli</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -27437,6 +28352,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauli</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -27603,6 +28523,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Huancaspata</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -27759,6 +28684,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -27915,6 +28845,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -28067,6 +29002,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -28223,6 +29163,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -28379,6 +29324,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -28535,6 +29485,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -28691,6 +29646,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -28847,6 +29807,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -29003,6 +29968,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -29157,6 +30127,11 @@
       <c r="AH195" t="inlineStr">
         <is>
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
     </row>
@@ -29267,6 +30242,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -29375,6 +30355,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -29483,6 +30468,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -29583,6 +30573,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -29691,6 +30686,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -29799,6 +30799,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -29907,6 +30912,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -30015,6 +31025,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -30123,6 +31138,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -30231,6 +31251,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -30339,6 +31364,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -30447,6 +31477,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -30555,6 +31590,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -30663,6 +31703,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pativilca</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -30819,6 +31864,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -30973,6 +32023,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -31129,6 +32184,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -31285,6 +32345,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -31439,6 +32504,11 @@
       <c r="AH214" t="inlineStr">
         <is>
           <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
     </row>
@@ -31559,6 +32629,11 @@
           <t>UGEL PUTUMAYO</t>
         </is>
       </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Putumayo</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -31679,6 +32754,11 @@
           <t>UGEL PUTUMAYO</t>
         </is>
       </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Putumayo</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -31845,6 +32925,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saquena</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -32011,6 +33096,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saquena</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -32177,6 +33267,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saquena</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -32341,6 +33436,11 @@
       <c r="AH220" t="inlineStr">
         <is>
           <t>UGEL MANU</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -32481,6 +33581,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -32647,6 +33752,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -32813,6 +33923,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -32979,6 +34094,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -33145,6 +34265,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -33311,6 +34436,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -33477,6 +34607,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -33643,6 +34778,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -33809,6 +34949,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -33975,6 +35120,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -34141,6 +35291,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -34291,6 +35446,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -34455,6 +35615,11 @@
       <c r="AH233" t="inlineStr">
         <is>
           <t>UGEL MANU</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -34595,6 +35760,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -34761,6 +35931,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -34927,6 +36102,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -35093,6 +36273,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -35257,6 +36442,11 @@
       <c r="AH238" t="inlineStr">
         <is>
           <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -35397,6 +36587,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -35563,6 +36758,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -35729,6 +36929,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -35879,6 +37084,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -36045,6 +37255,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -36209,6 +37424,11 @@
       <c r="AH244" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -36349,6 +37569,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -36487,6 +37712,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -36625,6 +37855,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -36789,6 +38024,11 @@
       <c r="AH248" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -36929,6 +38169,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -37093,6 +38338,11 @@
       <c r="AH250" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -37233,6 +38483,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -37371,6 +38626,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -37537,6 +38797,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -37703,6 +38968,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -37867,6 +39137,11 @@
       <c r="AH255" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -38007,6 +39282,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -38173,6 +39453,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -38321,6 +39606,11 @@
       <c r="AH258" t="inlineStr">
         <is>
           <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -38461,6 +39751,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -38611,6 +39906,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -38775,6 +40075,11 @@
       <c r="AH261" t="inlineStr">
         <is>
           <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -38915,6 +40220,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -39065,6 +40375,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -39213,6 +40528,11 @@
       <c r="AH264" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -39353,6 +40673,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -39501,6 +40826,11 @@
       <c r="AH266" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -39641,6 +40971,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -39789,6 +41124,11 @@
       <c r="AH268" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -39929,6 +41269,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -40079,6 +41424,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -40243,6 +41593,11 @@
       <c r="AH271" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -40383,6 +41738,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -40547,6 +41907,11 @@
       <c r="AH273" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -40687,6 +42052,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -40851,6 +42221,11 @@
       <c r="AH275" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -40991,6 +42366,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -41157,6 +42537,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -41307,6 +42692,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -41473,6 +42863,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -41639,6 +43034,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -41805,6 +43205,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -41969,6 +43374,11 @@
       <c r="AH282" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -42109,6 +43519,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -42247,6 +43662,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -42385,6 +43805,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -42551,6 +43976,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -42717,6 +44147,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -42883,6 +44318,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -43047,6 +44487,11 @@
       <c r="AH289" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -43187,6 +44632,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -43351,6 +44801,11 @@
       <c r="AH291" t="inlineStr">
         <is>
           <t>UGEL MANU</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -43491,6 +44946,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -43629,6 +45089,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -43777,6 +45242,11 @@
       <c r="AH294" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI294" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -43917,6 +45387,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -44055,6 +45530,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -44193,6 +45673,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -44357,6 +45842,11 @@
       <c r="AH298" t="inlineStr">
         <is>
           <t>UGEL MANU</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -44497,6 +45987,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -44635,6 +46130,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -44783,6 +46283,11 @@
       <c r="AH301" t="inlineStr">
         <is>
           <t>UGEL MANU</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
     </row>
@@ -44923,6 +46428,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -45061,6 +46571,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -45199,6 +46714,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -45347,6 +46867,11 @@
       <c r="AH305" t="inlineStr">
         <is>
           <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
     </row>
@@ -45487,6 +47012,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -45625,6 +47155,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -45789,6 +47324,11 @@
       <c r="AH308" t="inlineStr">
         <is>
           <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
     </row>
@@ -45929,6 +47469,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -46077,6 +47622,11 @@
       <c r="AH310" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -46217,6 +47767,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -46355,6 +47910,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -46521,6 +48081,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -46685,6 +48250,11 @@
       <c r="AH314" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -46825,6 +48395,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -46991,6 +48566,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -47153,6 +48733,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -47315,6 +48900,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -47481,6 +49071,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -47629,6 +49224,11 @@
       <c r="AH320" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -47769,6 +49369,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -47907,6 +49512,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -48045,6 +49655,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -48195,6 +49810,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -48345,6 +49965,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -48509,6 +50134,11 @@
       <c r="AH326" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -48649,6 +50279,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -48815,6 +50450,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -48979,6 +50619,11 @@
       <c r="AH329" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -49119,6 +50764,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -49283,6 +50933,11 @@
       <c r="AH331" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -49423,6 +51078,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -49585,6 +51245,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -49747,6 +51412,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -49911,6 +51581,11 @@
       <c r="AH335" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -50051,6 +51726,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -50211,6 +51891,11 @@
       <c r="AH337" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -50351,6 +52036,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -50489,6 +52179,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -50653,6 +52348,11 @@
       <c r="AH340" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -50797,6 +52497,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -50939,6 +52644,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -51095,6 +52805,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Algarrobal</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -51251,6 +52966,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Algarrobal</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -51405,6 +53125,11 @@
       <c r="AH345" t="inlineStr">
         <is>
           <t>UGEL PASCO</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
     </row>
@@ -51551,6 +53276,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -51695,6 +53425,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -51839,6 +53574,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -51995,6 +53735,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI349" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -52151,6 +53896,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -52307,6 +54057,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -52463,6 +54218,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -52619,6 +54379,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -52773,6 +54538,11 @@
       <c r="AH354" t="inlineStr">
         <is>
           <t>UGEL PASCO</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
     </row>
@@ -52881,6 +54651,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI355" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -52989,6 +54764,11 @@
       <c r="AH356" t="inlineStr">
         <is>
           <t>UGEL PIURA</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
     </row>
@@ -53097,6 +54877,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -53203,6 +54988,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -53309,6 +55099,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -53415,6 +55210,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -53521,6 +55321,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -53631,6 +55436,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -53779,6 +55589,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yorongos</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -53919,6 +55734,11 @@
       <c r="AH364" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -54071,6 +55891,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -54229,6 +56054,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -54387,6 +56217,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -54543,6 +56378,11 @@
       <c r="AH368" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -54693,6 +56533,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -54849,6 +56694,11 @@
       <c r="AH370" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI370" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -54999,6 +56849,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -55153,6 +57008,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -55307,6 +57167,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -55461,6 +57326,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -55615,6 +57485,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -55781,6 +57656,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -55937,6 +57817,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -56093,6 +57978,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -56249,6 +58139,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -56403,6 +58298,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -56559,6 +58459,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -56713,6 +58618,11 @@
       <c r="AH382" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
     </row>
@@ -56827,6 +58737,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -56981,6 +58896,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI384" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -57131,6 +59051,11 @@
       <c r="AH385" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -57285,6 +59210,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -57437,6 +59367,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI387" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -57579,6 +59514,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AI388" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -57729,6 +59669,11 @@
       <c r="AH389" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -57881,6 +59826,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI390" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -58031,6 +59981,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI391" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -58181,6 +60136,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI392" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -58331,6 +60291,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI393" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -58481,6 +60446,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -58631,6 +60601,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI395" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -58781,6 +60756,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -58931,6 +60911,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI397" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -59081,6 +61066,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI398" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -59231,6 +61221,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -59379,6 +61374,11 @@
       <c r="AH400" t="inlineStr">
         <is>
           <t>UGEL TARATA</t>
+        </is>
+      </c>
+      <c r="AI400" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
     </row>
@@ -59499,6 +61499,11 @@
       <c r="AH401" t="inlineStr">
         <is>
           <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
+      <c r="AI401" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ucayali</t>
         </is>
       </c>
     </row>
@@ -59613,6 +61618,11 @@
           <t>UGEL PADRE ABAD</t>
         </is>
       </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Ucayali</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -59779,6 +61789,11 @@
           <t>UGEL ATALAYA</t>
         </is>
       </c>
+      <c r="AI403" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sepahua</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -59945,6 +61960,11 @@
           <t>UGEL ATALAYA</t>
         </is>
       </c>
+      <c r="AI404" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sepahua</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -60109,6 +62129,11 @@
       <c r="AH405" t="inlineStr">
         <is>
           <t>UGEL ATALAYA</t>
+        </is>
+      </c>
+      <c r="AI405" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sepahua</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI405"/>
+  <dimension ref="A1:AK405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,16 @@
         </is>
       </c>
       <c r="AI1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -702,6 +712,16 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>18010</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -815,6 +835,16 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>18011</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -928,6 +958,16 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1041,6 +1081,16 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>18012</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1154,6 +1204,16 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
+          <t>18013</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1267,6 +1327,16 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
+          <t>18014</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1380,6 +1450,16 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
+          <t>18015</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1533,6 +1613,16 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
+          <t>019 CONSUELO DE JESUS SALAZAR ROJAS</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1693,6 +1783,16 @@
         </is>
       </c>
       <c r="AI10" t="inlineStr">
+        <is>
+          <t>PRITE DAVID/18003 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
@@ -1807,6 +1907,16 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
+          <t>028 MIGUELITO ALBERTO REYNA ZUBIATE/18255 LEONCIO PRADO</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -1977,6 +2087,16 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
+        <is>
+          <t>LOS ANGELES DE PEDRO CASTRO/18006</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
@@ -2135,6 +2255,16 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
+          <t>379 MUNDO MAGICO/379 MUNDO MAGICO</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -2296,6 +2426,16 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
+          <t>068 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -2457,6 +2597,16 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>18491 PROFESOR MANUEL ANTONIO ANGULO REYES</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Amazonas</t>
         </is>
       </c>
@@ -2618,6 +2768,16 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Huambo</t>
         </is>
       </c>
@@ -2779,6 +2939,16 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -2938,6 +3108,16 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3097,6 +3277,16 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3256,6 +3446,16 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3415,6 +3615,16 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3574,6 +3784,16 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3733,6 +3953,16 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -3892,6 +4122,16 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4053,6 +4293,16 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4212,6 +4462,16 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
+          <t>18052 PADRE BLAS VALERA PEREZ/18052 PADRE BLAS VALERA PEREZ</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4371,6 +4631,16 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
+          <t>18052 PADRE BLAS VALERA PEREZ/18052 PADRE BLAS VALERA PEREZ</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4530,6 +4800,16 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
+          <t>18052 PADRE BLAS VALERA PEREZ/18052 PADRE BLAS VALERA PEREZ</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4691,6 +4971,16 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
+          <t>18052 PADRE BLAS VALERA PEREZ/18052 PADRE BLAS VALERA PEREZ</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Levanto</t>
         </is>
       </c>
@@ -4843,6 +5133,16 @@
         </is>
       </c>
       <c r="AI30" t="inlineStr">
+        <is>
+          <t>18209</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Luya</t>
         </is>
@@ -5001,6 +5301,16 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Luya</t>
         </is>
       </c>
@@ -5162,6 +5472,16 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huari</t>
         </is>
       </c>
@@ -5323,6 +5643,16 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huari</t>
         </is>
       </c>
@@ -5483,6 +5813,16 @@
         </is>
       </c>
       <c r="AI34" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huari</t>
         </is>
@@ -5602,14 +5942,24 @@
           <t>MP Huari</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr">
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huari</t>
         </is>
@@ -5728,6 +6078,16 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
+          <t>86692 JUAN BAUTISTA DE LA SALLE/86692 JUAN BAUTISTA DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -5885,6 +6245,16 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
+          <t>86502 SAN SANTIAGO/86502 SAN SANTIAGO</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6034,6 +6404,16 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
+          <t>86547 DAVID ELWIN JOHNSON MILLER/86547 DAVID ELWIN JHONSON MILLER/86547 DAVID ELWIN JHONSON MILLER</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6191,6 +6571,16 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
+          <t>86548 JOSE MARIA VELAZ/86548 JOSE MARIA VELAZ/86548 JOSE MARIA VELAZ</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6348,6 +6738,16 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
+          <t>86732/86732/86732</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6505,6 +6905,16 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
+          <t>86733/86733/86733</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6662,6 +7072,16 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
+          <t>86769 ABRAHAM VALDELOMAR/86769 ABRAHAM VALDELOMAR/86769 ABRAHAM VALDELOMAR</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6819,6 +7239,16 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
+          <t>86825/86825</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pamparomas</t>
         </is>
       </c>
@@ -6980,6 +7410,16 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
+          <t>89554/89554</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -7141,6 +7581,16 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
+          <t>89556/89556/89556</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -7301,6 +7751,16 @@
         </is>
       </c>
       <c r="AI46" t="inlineStr">
+        <is>
+          <t>86648 SANTO DOMINGO DE GUZMAN/86648 SANTO DOMINGO DE GUZMAN</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -7419,6 +7879,16 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
+          <t>86618/86618</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -7580,6 +8050,16 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
+          <t>86649/86649/86649</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -7741,6 +8221,16 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
+          <t>86026 SANTA INES</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -7899,6 +8389,16 @@
         </is>
       </c>
       <c r="AI50" t="inlineStr">
+        <is>
+          <t>86026 SANTA INES</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
@@ -8017,6 +8517,16 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
+          <t>SANTISIMA VIRGEN DE GUADALUPE/SANTISIMA VIRGEN DE GUADALUPE/86026 SANTA INES/SANTA INES/SANTA INES</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -8178,6 +8688,16 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Yungay</t>
         </is>
       </c>
@@ -8339,6 +8859,16 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -8500,6 +9030,16 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -8661,6 +9201,16 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
+          <t>54493</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -8822,6 +9372,16 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
+          <t>54082 SEMILLAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -8983,6 +9543,16 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
+          <t>54557</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -9144,6 +9714,16 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -9305,6 +9885,16 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
+          <t>FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -9466,6 +10056,16 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
+          <t>SEÑOR DE HUANCA</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -9627,6 +10227,16 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
       </c>
@@ -9787,6 +10397,16 @@
         </is>
       </c>
       <c r="AI62" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Andarapa</t>
         </is>
@@ -9935,6 +10555,16 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
+          <t>54097</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Kaquiabamba</t>
         </is>
       </c>
@@ -10096,6 +10726,16 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
+          <t>54098 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Kaquiabamba</t>
         </is>
       </c>
@@ -10256,6 +10896,16 @@
         </is>
       </c>
       <c r="AI65" t="inlineStr">
+        <is>
+          <t>54142</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Kaquiabamba</t>
         </is>
@@ -10372,6 +11022,16 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
+          <t>54653</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Kaquiabamba</t>
         </is>
       </c>
@@ -10533,6 +11193,16 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
+          <t>40035 V. A. BELAUNDE/40035 V. A. BELAUNDE</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -10694,6 +11364,16 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
+          <t>40056 HORACIO ZEVALLOS GAMEZ/40056 HORACIO ZEBALLOS GAMEZ/40056 HORACIO ZEVALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -10853,6 +11533,16 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
+          <t>TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11012,6 +11702,16 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
+          <t>40057 SANTISIMA VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11171,6 +11871,16 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
+          <t>VICTOR ANDRES BELAUNDE</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11330,6 +12040,16 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
+          <t>40061 ESTADO DE SUECIA/40061 ESTADO DE SUECIA</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11489,6 +12209,16 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
+          <t>40106 JUAN SANTOS ATAHUALPA/40106 JUAN SANTOS ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11648,6 +12378,16 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
+          <t>JOSE SANTOS ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11809,6 +12549,16 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
+          <t>40173 DIVINO NIÑO JESUS/40173 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -11968,6 +12718,16 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
+          <t>40055 ROMEO LUNA VICTORIA/40055 ROMEO LUNA VICTORIA</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cerro Colorado</t>
         </is>
       </c>
@@ -12121,6 +12881,16 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
+          <t>40237</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -12274,6 +13044,16 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
+          <t>40239 NICOLAS DE PIEROLA/40239 NICOLAS DE PIEROLA</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -12427,6 +13207,16 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
+          <t>40249</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -12580,6 +13370,16 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
+          <t>40251 VIRGEN DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -12733,6 +13533,16 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
+          <t>SAN GREGORIO</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -12886,6 +13696,16 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
+          <t>SAN JACINTO</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -13039,6 +13859,16 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
+          <t>HACIENDA EL MEDIO</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
       </c>
@@ -13191,6 +14021,16 @@
         </is>
       </c>
       <c r="AI84" t="inlineStr">
+        <is>
+          <t>GOTITAS DE AMOR</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Nicolas de Pierola</t>
         </is>
@@ -13305,6 +14145,16 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
+          <t>ALBERTO FLORES GALINDO/ALBERTO FLORES GALINDO</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Orcopampa</t>
         </is>
       </c>
@@ -13417,6 +14267,16 @@
         </is>
       </c>
       <c r="AI86" t="inlineStr">
+        <is>
+          <t>40702 ALBERTO BENAVIDES DE LA QUINTANA/40702 ALBERTO BENAVIDES DE LA QUINTANA/40702 ALBERTO BENAVIDES DE LA QUINTANA</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Orcopampa</t>
         </is>
@@ -13527,6 +14387,16 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
+          <t>40074 JOSE L. BUSTAMANTE Y RIVERO/40074 JOSE L. BUSTAMANTE Y RIVERO</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -13636,6 +14506,16 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
+          <t>40075 HORACIO MORALES DELGADO/40075 HORACIO MORALES DELGADO</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -13744,6 +14624,16 @@
         </is>
       </c>
       <c r="AI89" t="inlineStr">
+        <is>
+          <t>40078 SAGRADO CORAZON DE JESUS DE SACHACA</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
@@ -13852,6 +14742,16 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
+          <t>40079 VICTOR NUÑEZ VALENCIA/40079 VICTOR NUÑEZ VALENCIA</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -13959,6 +14859,16 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
+          <t>40660 DOMINIC WILLIAMS</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14066,6 +14976,16 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
+          <t>40672 DOREEN CABRERA DE WILLIANS</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14175,6 +15095,16 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
+          <t>ALTO DE AMADOS</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14284,6 +15214,16 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
+          <t>CHIRIGUANA</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14393,6 +15333,16 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
+          <t>HUARANGUILLO</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14502,6 +15452,16 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
+          <t>SANTA GERTRUDIS</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14610,6 +15570,16 @@
         </is>
       </c>
       <c r="AI97" t="inlineStr">
+        <is>
+          <t>VILLA EL TRIUNFO</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
@@ -14718,6 +15688,16 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
+          <t>EL MILAGRO DE FATIMA/EL MILAGRO DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sachaca</t>
         </is>
       </c>
@@ -14879,6 +15859,16 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
+          <t>40088 REYNO DE BELGICA/40088 REYNO DE BELGICA</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
@@ -15040,6 +16030,16 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
+          <t>40091 ALMA MATER DE CONGATA/40091 ALMA MATER DE CONGATA</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
@@ -15201,6 +16201,16 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
+          <t>CERRO VERDE</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
@@ -15362,6 +16372,16 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
+          <t>ALVAREZ THOMAS</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
@@ -15523,6 +16543,16 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
+          <t>MANITOS DE XIOMARA</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
       </c>
@@ -15683,6 +16713,16 @@
         </is>
       </c>
       <c r="AI104" t="inlineStr">
+        <is>
+          <t>DULCES BROTECITOS</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Uchumayo</t>
         </is>
@@ -15841,6 +16881,16 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
+          <t>40202 CHARLOTTE/40202 CHARLOTTE/40202 CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -15996,6 +17046,16 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
+          <t>40202 CHARLOTTE/40202 CHARLOTTE/40202 CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16153,6 +17213,16 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
+          <t>CIUDAD DE DIOS KM 16</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16308,6 +17378,16 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
+          <t>CIUDAD DE DIOS KM 16</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16465,6 +17545,16 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
+          <t>LUCERITO DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16622,6 +17712,16 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
+          <t>EL ALTIPLANO/EL ALTIPLANO</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16777,6 +17877,16 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
+          <t>EL ALTIPLANO/EL ALTIPLANO</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -16934,6 +18044,16 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
+          <t>SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO/SANTO TORIBIO DE MOGROVEJO</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -17091,6 +18211,16 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
+          <t>JARDIN DEL COLCA/JARDIN DEL COLCA/JARDIN DEL COLCA</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yura</t>
         </is>
       </c>
@@ -17252,6 +18382,16 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
+          <t>ARTURO OSORES CABRERA</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Anguia</t>
         </is>
       </c>
@@ -17413,6 +18553,16 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Conchan</t>
         </is>
       </c>
@@ -17564,6 +18714,16 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
+          <t>821136</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -17715,6 +18875,16 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
+          <t>82157</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -17866,6 +19036,16 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
+          <t>82914/82914</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -18017,6 +19197,16 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -18168,6 +19358,16 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
+          <t>BELLA UNION JESUS MARIA</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -18319,6 +19519,16 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
+          <t>JAVIER PRADO</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Encañada</t>
         </is>
       </c>
@@ -18480,6 +19690,16 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -18641,6 +19861,16 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
+          <t>10432</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -18802,6 +20032,16 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
+          <t>ANAXIMANDRO VEGA/10433</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -18963,6 +20203,16 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
+          <t>ANAXIMANDRO VEGA</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -19124,6 +20374,16 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
+          <t>SAMUEL DEL ALCAZAR</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -19285,6 +20545,16 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
+          <t>JOSE ANTONIO ENCINAS</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -19446,6 +20716,16 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
+          <t>TUPAC AMARU II</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Lajas</t>
         </is>
       </c>
@@ -19613,6 +20893,16 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
+          <t>FERMIN AVILA</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -19769,6 +21059,16 @@
         </is>
       </c>
       <c r="AI130" t="inlineStr">
+        <is>
+          <t>5098 KUMAMOTO/5098 KUMAMOTO</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
@@ -19873,6 +21173,16 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
+          <t>MANUEL SEOANE CORRALES/MANUEL SEOANE CORRALES/MANUEL SEOANE CORRALES/MANUEL SEOANE CORRALES</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -20034,6 +21344,16 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
+          <t>5119 VILLA EMILIA</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -20204,6 +21524,16 @@
         </is>
       </c>
       <c r="AI133" t="inlineStr">
+        <is>
+          <t>FE Y ALEGRIA 33/FE Y ALEGRIA 33/FE Y ALEGRIA 33</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
@@ -20352,6 +21682,16 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
+          <t>124 VILLA DEL MAR</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -20504,6 +21844,16 @@
         </is>
       </c>
       <c r="AI135" t="inlineStr">
+        <is>
+          <t>5151 SAN JUAN BOSCO</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
@@ -20652,6 +22002,16 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -20809,6 +22169,16 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
+          <t>167 CRISTO REY DE LOS NIÑOS</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -20970,6 +22340,16 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
+          <t>VIRGEN NATIVIDAD</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ccapi</t>
         </is>
       </c>
@@ -21141,6 +22521,16 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -21312,6 +22702,16 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
+          <t>MONSEÑOR JAVIER ARIZ/50294</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -21467,6 +22867,16 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -21638,6 +23048,16 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
+          <t>64446</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -21809,6 +23229,16 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
+          <t>64449</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -21970,6 +23400,16 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
+          <t>821/64450</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -22141,6 +23581,16 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
+          <t>JUAN SANTOS ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -22302,6 +23752,16 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
+          <t>52112</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -22473,6 +23933,16 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Megantoni</t>
         </is>
       </c>
@@ -22634,6 +24104,16 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
+          <t>56242</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pallpata</t>
         </is>
       </c>
@@ -22801,6 +24281,16 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
+          <t>38317 SEMILLITAS DEL FUTURO/38317 SEMILLITAS DEL FUTURO</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -22968,6 +24458,16 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
+          <t>38831/38831</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23135,6 +24635,16 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
+          <t>38838 CAPITAN FAP JOSE ABELARDO QUIÑONES GONZALES</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23294,6 +24804,16 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
+          <t>38776/38776</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23453,6 +24973,16 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
+          <t>501345/501345</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23612,6 +25142,16 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
+          <t>38632 SIMON BOLIVAR/38632 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23779,6 +25319,16 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -23946,6 +25496,16 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
+          <t>501445/501445</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
       </c>
@@ -24104,6 +25664,16 @@
         </is>
       </c>
       <c r="AI157" t="inlineStr">
+        <is>
+          <t>1369 ISAAC NEWTON/1369 ISAAC NEWTON</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pichari</t>
         </is>
@@ -24254,6 +25824,16 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Quiquijana</t>
         </is>
       </c>
@@ -24415,6 +25995,16 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
+          <t>124 BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -24575,6 +26165,16 @@
         </is>
       </c>
       <c r="AI160" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
@@ -24725,6 +26325,16 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
+          <t>36225</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -24886,6 +26496,16 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
+          <t>36273/36273</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25047,6 +26667,16 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
+          <t>36274</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25208,6 +26838,16 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
+          <t>36275</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25379,6 +27019,16 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
+          <t>36398</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25540,6 +27190,16 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
+          <t>36415</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25701,6 +27361,16 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
+          <t>JESUS NAZARENO</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -25872,6 +27542,16 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
+          <t>GUZMAN SERAFICO SOTO/GUZMAN SERAFICO SOTO</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Francisco de Asis</t>
         </is>
       </c>
@@ -26033,6 +27713,16 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -26194,6 +27884,16 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
+          <t>22754/22754</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -26355,6 +28055,16 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -26516,6 +28226,16 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Pisco</t>
         </is>
       </c>
@@ -26677,6 +28397,16 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
+          <t>22464 REPUBLICA ARGENTINA/22464 REPUBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Pisco</t>
         </is>
       </c>
@@ -26838,6 +28568,16 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
+          <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Pisco</t>
         </is>
       </c>
@@ -26999,6 +28739,16 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
+          <t>907 VIRGEN DEL ROSARIO DE YAUCA</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Pisco</t>
         </is>
       </c>
@@ -27148,6 +28898,16 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
+          <t>501/22324</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pueblo Nuevo</t>
         </is>
       </c>
@@ -27319,6 +29079,16 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
+          <t>30660</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -27490,6 +29260,16 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
+          <t>30663</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -27661,6 +29441,16 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
+          <t>30664</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -27832,6 +29622,16 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
+          <t>30760</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
       </c>
@@ -28002,6 +29802,16 @@
         </is>
       </c>
       <c r="AI181" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Llaylla</t>
         </is>
@@ -28120,6 +29930,16 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
+          <t>424 CARRUSEL</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauli</t>
         </is>
       </c>
@@ -28237,6 +30057,16 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
+          <t>30482 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauli</t>
         </is>
       </c>
@@ -28354,6 +30184,16 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
+          <t>30568</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauli</t>
         </is>
       </c>
@@ -28525,6 +30365,16 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
+          <t>80739</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Huancaspata</t>
         </is>
       </c>
@@ -28686,6 +30536,16 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
+          <t>0009 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -28847,6 +30707,16 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
+          <t>0038 VIRGEN MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29004,6 +30874,16 @@
       </c>
       <c r="AI188" t="inlineStr">
         <is>
+          <t>0051 LOS PASTORCITOS DE NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29165,6 +31045,16 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
+          <t>136 SANTA ROSA MILAGROSA/136 SANTA ROSA MILAGROSA/136 SANTA ROSA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29326,6 +31216,16 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
+          <t>27 DE MARZO/27 DE MARZO</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29487,6 +31387,16 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
+          <t>NIÑO MANUELITO - A</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29648,6 +31558,16 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
+          <t>PASITOS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29809,6 +31729,16 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
+          <t>JOYITAS DE JESUS</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -29970,6 +31900,16 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -30130,6 +32070,16 @@
         </is>
       </c>
       <c r="AI195" t="inlineStr">
+        <is>
+          <t>CAMINITO DE MOTUPE</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 05 - LIMA METROPOLITANA</t>
         </is>
@@ -30244,6 +32194,16 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30357,6 +32317,16 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30470,6 +32440,16 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30575,6 +32555,16 @@
       </c>
       <c r="AI199" t="inlineStr">
         <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30688,6 +32678,16 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
+          <t>649-01</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30801,6 +32801,16 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
+          <t>20501 SANTA ROSA/20501 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -30914,6 +32924,16 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
+          <t>PATIVILCA/PATIVILCA/20505 VIRGEN INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31027,6 +33047,16 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
+          <t>20506 JOSE A ENCINAS FRANCO/20506 JOSE A ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31140,6 +33170,16 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
+          <t>20832/20832</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31253,6 +33293,16 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
+          <t>21575</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31366,6 +33416,16 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
+          <t>21579 ROSA SOTO DE MANRRIQUE/646 ROSA SOTO DE MANRIQUE/21579 ROSA SOTO DE MANRRIQUE</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31479,6 +33539,16 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
+          <t>20504 SAN JERONIMO/20504 SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31592,6 +33662,16 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
+          <t>JOSE PARDO Y BARREDA</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31705,6 +33785,16 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pativilca</t>
         </is>
       </c>
@@ -31866,6 +33956,16 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
+          <t>20354 MANUEL EMILIO SCORZA TORRES</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -32025,6 +34125,16 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
+          <t>20354 MANUEL EMILIO SCORZA TORRES</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -32186,6 +34296,16 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
+          <t>20857/664/20857</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -32347,6 +34467,16 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -32507,6 +34637,16 @@
         </is>
       </c>
       <c r="AI214" t="inlineStr">
+        <is>
+          <t>20880 ALCIBIADES FERNANDEZ GUERRERO</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
@@ -32631,6 +34771,16 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
+          <t>166 MARIA ANGELICA SOUSA MANIHUARI</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
       </c>
@@ -32756,6 +34906,16 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Putumayo</t>
         </is>
       </c>
@@ -32927,6 +35087,16 @@
       </c>
       <c r="AI217" t="inlineStr">
         <is>
+          <t>60630</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saquena</t>
         </is>
       </c>
@@ -33098,6 +35268,16 @@
       </c>
       <c r="AI218" t="inlineStr">
         <is>
+          <t>60692/60692</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saquena</t>
         </is>
       </c>
@@ -33269,6 +35449,16 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
+          <t>60916</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saquena</t>
         </is>
       </c>
@@ -33439,6 +35629,16 @@
         </is>
       </c>
       <c r="AI220" t="inlineStr">
+        <is>
+          <t>345 BOCA MANU</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -33583,6 +35783,16 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
+          <t>50875</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -33754,6 +35964,16 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -33925,6 +36145,16 @@
       </c>
       <c r="AI223" t="inlineStr">
         <is>
+          <t>DIAMANTE</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34096,6 +36326,16 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
+          <t>52245</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34267,6 +36507,16 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34438,6 +36688,16 @@
       </c>
       <c r="AI226" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34609,6 +36869,16 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34780,6 +37050,16 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
+          <t>50843</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34951,6 +37231,16 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
+          <t>52200</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35122,6 +37412,16 @@
       </c>
       <c r="AI230" t="inlineStr">
         <is>
+          <t>52133</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35293,6 +37593,16 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
+          <t>CIENCIAS DE NUEVA/52159 CIENCIAS DE NUEVA</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35448,6 +37758,16 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
+          <t>332 DOCE DE ENERO</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35618,6 +37938,16 @@
         </is>
       </c>
       <c r="AI233" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -35762,6 +38092,16 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
+          <t>260 LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35933,6 +38273,16 @@
       </c>
       <c r="AI235" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36104,6 +38454,16 @@
       </c>
       <c r="AI236" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36275,6 +38635,16 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36445,6 +38815,16 @@
         </is>
       </c>
       <c r="AI238" t="inlineStr">
+        <is>
+          <t>53004 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -36589,6 +38969,16 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
+          <t>DOS DE MAYO/DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36760,6 +39150,16 @@
       </c>
       <c r="AI240" t="inlineStr">
         <is>
+          <t>EL ARCA DE PACAHUARA/52216 EL ARCA DE PACAHUARA</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36931,6 +39331,16 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -37086,6 +39496,16 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -37257,6 +39677,16 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -37427,6 +39857,16 @@
         </is>
       </c>
       <c r="AI244" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -37571,6 +40011,16 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR/SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -37714,6 +40164,16 @@
       </c>
       <c r="AI246" t="inlineStr">
         <is>
+          <t>52042/52042</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -37857,6 +40317,16 @@
       </c>
       <c r="AI247" t="inlineStr">
         <is>
+          <t>52072 MARIO VARGAS LLOSA/52072 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38027,6 +40497,16 @@
         </is>
       </c>
       <c r="AI248" t="inlineStr">
+        <is>
+          <t>52077/52077</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -38171,6 +40651,16 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
+          <t>52114</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38341,6 +40831,16 @@
         </is>
       </c>
       <c r="AI250" t="inlineStr">
+        <is>
+          <t>52129</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -38485,6 +40985,16 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
+          <t>52219/52219</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38628,6 +41138,16 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38799,6 +41319,16 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38970,6 +41500,16 @@
       </c>
       <c r="AI254" t="inlineStr">
         <is>
+          <t>368 NIÑOS DE LA SELVA</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39140,6 +41680,16 @@
         </is>
       </c>
       <c r="AI255" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -39284,6 +41834,16 @@
       </c>
       <c r="AI256" t="inlineStr">
         <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39455,6 +42015,16 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
+          <t>NUEVA AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39609,6 +42179,16 @@
         </is>
       </c>
       <c r="AI258" t="inlineStr">
+        <is>
+          <t>52055</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -39753,6 +42333,16 @@
       </c>
       <c r="AI259" t="inlineStr">
         <is>
+          <t>52144</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -39908,6 +42498,16 @@
       </c>
       <c r="AI260" t="inlineStr">
         <is>
+          <t>IÑAPARI</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -40078,6 +42678,16 @@
         </is>
       </c>
       <c r="AI261" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -40222,6 +42832,16 @@
       </c>
       <c r="AI262" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -40377,6 +42997,16 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
+          <t>52062 JAVIER HERAUD/52062 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40531,6 +43161,16 @@
         </is>
       </c>
       <c r="AI264" t="inlineStr">
+        <is>
+          <t>52033/52033</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -40675,6 +43315,16 @@
       </c>
       <c r="AI265" t="inlineStr">
         <is>
+          <t>52039</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40829,6 +43479,16 @@
         </is>
       </c>
       <c r="AI266" t="inlineStr">
+        <is>
+          <t>52105</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -40973,6 +43633,16 @@
       </c>
       <c r="AI267" t="inlineStr">
         <is>
+          <t>52132</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41127,6 +43797,16 @@
         </is>
       </c>
       <c r="AI268" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -41271,6 +43951,16 @@
       </c>
       <c r="AI269" t="inlineStr">
         <is>
+          <t>382 PEQUEÑAS GOTAS DE VIDA</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41426,6 +44116,16 @@
       </c>
       <c r="AI270" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41596,6 +44296,16 @@
         </is>
       </c>
       <c r="AI271" t="inlineStr">
+        <is>
+          <t>52262 CARLOS MARQUEZ BRAGA</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -41740,6 +44450,16 @@
       </c>
       <c r="AI272" t="inlineStr">
         <is>
+          <t>ALEJANDRO TOLEDO</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41910,6 +44630,16 @@
         </is>
       </c>
       <c r="AI273" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -42054,6 +44784,16 @@
       </c>
       <c r="AI274" t="inlineStr">
         <is>
+          <t>286 CARITAS FELICES</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42224,6 +44964,16 @@
         </is>
       </c>
       <c r="AI275" t="inlineStr">
+        <is>
+          <t>HEROES DE ILLAMPU/HEROES DE ILLAMPU/HEROES DE ILLAMPU</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -42368,6 +45118,16 @@
       </c>
       <c r="AI276" t="inlineStr">
         <is>
+          <t>ALMIRANTE MIGUEL GRAU SEMINARIO/52094 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42539,6 +45299,16 @@
       </c>
       <c r="AI277" t="inlineStr">
         <is>
+          <t>52095/52095</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42694,6 +45464,16 @@
       </c>
       <c r="AI278" t="inlineStr">
         <is>
+          <t>52136</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42865,6 +45645,16 @@
       </c>
       <c r="AI279" t="inlineStr">
         <is>
+          <t>52242</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -43036,6 +45826,16 @@
       </c>
       <c r="AI280" t="inlineStr">
         <is>
+          <t>52137</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -43207,6 +46007,16 @@
       </c>
       <c r="AI281" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -43377,6 +46187,16 @@
         </is>
       </c>
       <c r="AI282" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -43521,6 +46341,16 @@
       </c>
       <c r="AI283" t="inlineStr">
         <is>
+          <t>435 NUEVA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -43664,6 +46494,16 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -43807,6 +46647,16 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -43978,6 +46828,16 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
+          <t>52075</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -44149,6 +47009,16 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
+          <t>52154</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -44320,6 +47190,16 @@
       </c>
       <c r="AI288" t="inlineStr">
         <is>
+          <t>PEDRO PAULET/PEDRO PAULET</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -44490,6 +47370,16 @@
         </is>
       </c>
       <c r="AI289" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -44634,6 +47524,16 @@
       </c>
       <c r="AI290" t="inlineStr">
         <is>
+          <t>52212</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -44804,6 +47704,16 @@
         </is>
       </c>
       <c r="AI291" t="inlineStr">
+        <is>
+          <t>DANIEL ALCIDES CARRION/DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -44948,6 +47858,16 @@
       </c>
       <c r="AI292" t="inlineStr">
         <is>
+          <t>PUNKIRI CHICO/52230</t>
+        </is>
+      </c>
+      <c r="AJ292" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK292" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -45091,6 +48011,16 @@
       </c>
       <c r="AI293" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -45245,6 +48175,16 @@
         </is>
       </c>
       <c r="AI294" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="AJ294" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK294" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -45389,6 +48329,16 @@
       </c>
       <c r="AI295" t="inlineStr">
         <is>
+          <t>326 PALOTOA</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -45532,6 +48482,16 @@
       </c>
       <c r="AI296" t="inlineStr">
         <is>
+          <t>52179</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -45675,6 +48635,16 @@
       </c>
       <c r="AI297" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI/50431 JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AJ297" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK297" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -45845,6 +48815,16 @@
         </is>
       </c>
       <c r="AI298" t="inlineStr">
+        <is>
+          <t>279 NIÑO DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -45989,6 +48969,16 @@
       </c>
       <c r="AI299" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -46132,6 +49122,16 @@
       </c>
       <c r="AI300" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -46286,6 +49286,16 @@
         </is>
       </c>
       <c r="AI301" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -46430,6 +49440,16 @@
       </c>
       <c r="AI302" t="inlineStr">
         <is>
+          <t>CIRILO ESPINAL SUAREZ</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -46573,6 +49593,16 @@
       </c>
       <c r="AI303" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -46716,6 +49746,16 @@
       </c>
       <c r="AI304" t="inlineStr">
         <is>
+          <t>52057</t>
+        </is>
+      </c>
+      <c r="AJ304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -46870,6 +49910,16 @@
         </is>
       </c>
       <c r="AI305" t="inlineStr">
+        <is>
+          <t>52061/52061</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -47014,6 +50064,16 @@
       </c>
       <c r="AI306" t="inlineStr">
         <is>
+          <t>OLLANTA HUMALA TASSO</t>
+        </is>
+      </c>
+      <c r="AJ306" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK306" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -47157,6 +50217,16 @@
       </c>
       <c r="AI307" t="inlineStr">
         <is>
+          <t>52093 JESUS DIVINO MAESTRO/52093 JESUS DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -47327,6 +50397,16 @@
         </is>
       </c>
       <c r="AI308" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AJ308" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK308" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -47471,6 +50551,16 @@
       </c>
       <c r="AI309" t="inlineStr">
         <is>
+          <t>264 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -47625,6 +50715,16 @@
         </is>
       </c>
       <c r="AI310" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="AJ310" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK310" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -47769,6 +50869,16 @@
       </c>
       <c r="AI311" t="inlineStr">
         <is>
+          <t>267 CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -47912,6 +51022,16 @@
       </c>
       <c r="AI312" t="inlineStr">
         <is>
+          <t>295 ARCO IRIS</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -48083,6 +51203,16 @@
       </c>
       <c r="AI313" t="inlineStr">
         <is>
+          <t>296 LAS PALMERAS</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -48253,6 +51383,16 @@
         </is>
       </c>
       <c r="AI314" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -48397,6 +51537,16 @@
       </c>
       <c r="AI315" t="inlineStr">
         <is>
+          <t>301 ESE EJA SHOI</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -48568,6 +51718,16 @@
       </c>
       <c r="AI316" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -48735,6 +51895,16 @@
       </c>
       <c r="AI317" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -48902,6 +52072,16 @@
       </c>
       <c r="AI318" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49073,6 +52253,16 @@
       </c>
       <c r="AI319" t="inlineStr">
         <is>
+          <t>318 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49227,6 +52417,16 @@
         </is>
       </c>
       <c r="AI320" t="inlineStr">
+        <is>
+          <t>LA PASTORA/LA PASTORA/LA PASTORA</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -49371,6 +52571,16 @@
       </c>
       <c r="AI321" t="inlineStr">
         <is>
+          <t>52011 SAN JUAN BAUTISTA/52011 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49514,6 +52724,16 @@
       </c>
       <c r="AI322" t="inlineStr">
         <is>
+          <t>52021</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49657,6 +52877,16 @@
       </c>
       <c r="AI323" t="inlineStr">
         <is>
+          <t>DOS DE MAYO/DOS DE MAYO/DOS DE MAYO/DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49812,6 +53042,16 @@
       </c>
       <c r="AI324" t="inlineStr">
         <is>
+          <t>SAN BERNARDO/52035</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -49967,6 +53207,16 @@
       </c>
       <c r="AI325" t="inlineStr">
         <is>
+          <t>52084</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK325" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -50137,6 +53387,16 @@
         </is>
       </c>
       <c r="AI326" t="inlineStr">
+        <is>
+          <t>433 ROBERTO GUILLERMO VELA VALLES/52183/52183</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -50281,6 +53541,16 @@
       </c>
       <c r="AI327" t="inlineStr">
         <is>
+          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO/APLICACION NUESTRA SEÑORA DEL ROSARIO/APLICACION NUESTRA SEÑORA DEL ROSARIO/NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -50452,6 +53722,16 @@
       </c>
       <c r="AI328" t="inlineStr">
         <is>
+          <t>SANTA RITA DE CASIA</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK328" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -50622,6 +53902,16 @@
         </is>
       </c>
       <c r="AI329" t="inlineStr">
+        <is>
+          <t>52225</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -50766,6 +54056,16 @@
       </c>
       <c r="AI330" t="inlineStr">
         <is>
+          <t>361 SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS/52181 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -50936,6 +54236,16 @@
         </is>
       </c>
       <c r="AI331" t="inlineStr">
+        <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -51080,6 +54390,16 @@
       </c>
       <c r="AI332" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -51247,6 +54567,16 @@
       </c>
       <c r="AI333" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK333" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -51414,6 +54744,16 @@
       </c>
       <c r="AI334" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK334" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -51584,6 +54924,16 @@
         </is>
       </c>
       <c r="AI335" t="inlineStr">
+        <is>
+          <t>400 LUCECITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -51728,6 +55078,16 @@
       </c>
       <c r="AI336" t="inlineStr">
         <is>
+          <t>344 MARIA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -51894,6 +55254,16 @@
         </is>
       </c>
       <c r="AI337" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK337" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -52038,6 +55408,16 @@
       </c>
       <c r="AI338" t="inlineStr">
         <is>
+          <t>52265 MARCELINO CHAMPAGNAT/52265 MARCELINO CHAMPAGNAT</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK338" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -52181,6 +55561,16 @@
       </c>
       <c r="AI339" t="inlineStr">
         <is>
+          <t>JARDIN TROPICAL/JARDIN TROPICAL</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK339" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -52351,6 +55741,16 @@
         </is>
       </c>
       <c r="AI340" t="inlineStr">
+        <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK340" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -52499,6 +55899,16 @@
       </c>
       <c r="AI341" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -52646,6 +56056,16 @@
       </c>
       <c r="AI342" t="inlineStr">
         <is>
+          <t>334 GOTITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -52807,6 +56227,16 @@
       </c>
       <c r="AI343" t="inlineStr">
         <is>
+          <t>43130 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="AJ343" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK343" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Algarrobal</t>
         </is>
       </c>
@@ -52968,6 +56398,16 @@
       </c>
       <c r="AI344" t="inlineStr">
         <is>
+          <t>360 SEMILLITAS DE OLIVO</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Algarrobal</t>
         </is>
       </c>
@@ -53128,6 +56568,16 @@
         </is>
       </c>
       <c r="AI345" t="inlineStr">
+        <is>
+          <t>34617 LUZ DEL SABER/34617 LUZ DEL SABER</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
@@ -53278,6 +56728,16 @@
       </c>
       <c r="AI346" t="inlineStr">
         <is>
+          <t>EL PALOMAR</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -53427,6 +56887,16 @@
       </c>
       <c r="AI347" t="inlineStr">
         <is>
+          <t>ANITA FERNANDINI</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK347" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -53576,6 +57046,16 @@
       </c>
       <c r="AI348" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -53737,6 +57217,16 @@
       </c>
       <c r="AI349" t="inlineStr">
         <is>
+          <t>34042</t>
+        </is>
+      </c>
+      <c r="AJ349" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK349" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -53898,6 +57388,16 @@
       </c>
       <c r="AI350" t="inlineStr">
         <is>
+          <t>34043 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK350" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -54059,6 +57559,16 @@
       </c>
       <c r="AI351" t="inlineStr">
         <is>
+          <t>34045</t>
+        </is>
+      </c>
+      <c r="AJ351" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK351" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -54220,6 +57730,16 @@
       </c>
       <c r="AI352" t="inlineStr">
         <is>
+          <t>34103 HEROES DEL 41</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -54381,6 +57901,16 @@
       </c>
       <c r="AI353" t="inlineStr">
         <is>
+          <t>REPUBLICA DE ARGENTINA</t>
+        </is>
+      </c>
+      <c r="AJ353" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK353" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -54541,6 +58071,16 @@
         </is>
       </c>
       <c r="AI354" t="inlineStr">
+        <is>
+          <t>EL TIGRE</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
@@ -54653,6 +58193,16 @@
       </c>
       <c r="AI355" t="inlineStr">
         <is>
+          <t>15014 MANUEL HIDALGO CARNERO/15014 MANUEL HIDALGO CARNERO</t>
+        </is>
+      </c>
+      <c r="AJ355" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK355" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -54767,6 +58317,16 @@
         </is>
       </c>
       <c r="AI356" t="inlineStr">
+        <is>
+          <t>15015 HEROES DEL CENEPA/15015 HEROES DEL CENEPA</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK356" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
@@ -54879,6 +58439,16 @@
       </c>
       <c r="AI357" t="inlineStr">
         <is>
+          <t>SANTISIMA VIRGEN DE GUADALUPE/SANTISIMA VIRGEN DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -54990,6 +58560,16 @@
       </c>
       <c r="AI358" t="inlineStr">
         <is>
+          <t>15185/15185</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK358" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -55101,6 +58681,16 @@
       </c>
       <c r="AI359" t="inlineStr">
         <is>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES/CAP. FAP JOSE ABELARDO QUIÑONES/CAP. FAP JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -55212,6 +58802,16 @@
       </c>
       <c r="AI360" t="inlineStr">
         <is>
+          <t>SAN JOSE DE TARBES/SAN JOSE DE TARBES</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -55323,6 +58923,16 @@
       </c>
       <c r="AI361" t="inlineStr">
         <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -55438,6 +59048,16 @@
       </c>
       <c r="AI362" t="inlineStr">
         <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -55591,6 +59211,16 @@
       </c>
       <c r="AI363" t="inlineStr">
         <is>
+          <t>WILFREDO EZEQUIEL PONCE CHIRINOS</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yorongos</t>
         </is>
       </c>
@@ -55737,6 +59367,16 @@
         </is>
       </c>
       <c r="AI364" t="inlineStr">
+        <is>
+          <t>42250 CESAR AUGUSTO COHAILA TAMAYO/42250 CESAR AUGUSTO COHAILA TAMAYO/CESAR AUGUSTO COHAILA TAMAYO/42250 CESAR AUGUSTO COHAILA TAMAYO</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -55893,6 +59533,16 @@
       </c>
       <c r="AI365" t="inlineStr">
         <is>
+          <t>473 PEDRO QUINA CASTAÑON/473 PEDRO QUINA CASTAÑON</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
         </is>
       </c>
@@ -56056,6 +59706,16 @@
       </c>
       <c r="AI366" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AJ366" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK366" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -56219,6 +59879,16 @@
       </c>
       <c r="AI367" t="inlineStr">
         <is>
+          <t>354 VIRGEN MARIA</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -56381,6 +60051,16 @@
         </is>
       </c>
       <c r="AI368" t="inlineStr">
+        <is>
+          <t>42053 BARTOLOME JULIO ROSPIGLIOSI</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -56535,6 +60215,16 @@
       </c>
       <c r="AI369" t="inlineStr">
         <is>
+          <t>42032 JOSE JOAQUIN INCLAN/42032 JOSE JOAQUIN INCLAN</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -56697,6 +60387,16 @@
         </is>
       </c>
       <c r="AI370" t="inlineStr">
+        <is>
+          <t>443 SANTA TERESITA/443 SANTA TERESITA</t>
+        </is>
+      </c>
+      <c r="AJ370" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK370" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -56851,6 +60551,16 @@
       </c>
       <c r="AI371" t="inlineStr">
         <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AJ371" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK371" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -57010,6 +60720,16 @@
       </c>
       <c r="AI372" t="inlineStr">
         <is>
+          <t>308 MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -57169,6 +60889,16 @@
       </c>
       <c r="AI373" t="inlineStr">
         <is>
+          <t>232 VIRGEN DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -57328,6 +61058,16 @@
       </c>
       <c r="AI374" t="inlineStr">
         <is>
+          <t>312 JESUS NAZARENO</t>
+        </is>
+      </c>
+      <c r="AJ374" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK374" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -57487,6 +61227,16 @@
       </c>
       <c r="AI375" t="inlineStr">
         <is>
+          <t>43505 GUSTAVO PONS MUZZO/43505 GUSTAVO PONS MUZZO</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -57658,6 +61408,16 @@
       </c>
       <c r="AI376" t="inlineStr">
         <is>
+          <t>314 VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -57819,6 +61579,16 @@
       </c>
       <c r="AI377" t="inlineStr">
         <is>
+          <t>353 NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -57980,6 +61750,16 @@
       </c>
       <c r="AI378" t="inlineStr">
         <is>
+          <t>380 LUIS CAVAGNARO ORELLANA</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -58141,6 +61921,16 @@
       </c>
       <c r="AI379" t="inlineStr">
         <is>
+          <t>42073 MARIA PILAR VILLANUEVA B</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK379" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -58300,6 +62090,16 @@
       </c>
       <c r="AI380" t="inlineStr">
         <is>
+          <t>42073 MARIA PILAR VILLANUEVA B</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -58461,6 +62261,16 @@
       </c>
       <c r="AI381" t="inlineStr">
         <is>
+          <t>42207 SAN PEDRO/42207 SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -58621,6 +62431,16 @@
         </is>
       </c>
       <c r="AI382" t="inlineStr">
+        <is>
+          <t>42072 CAROLINA FREYRE ARIAS/42072 CAROLINA FREYRE ARIAS</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
@@ -58739,6 +62559,16 @@
       </c>
       <c r="AI383" t="inlineStr">
         <is>
+          <t>42072 CAROLINA FREYRE ARIAS/42072 CAROLINA FREYRE ARIAS</t>
+        </is>
+      </c>
+      <c r="AJ383" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK383" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -58898,6 +62728,16 @@
       </c>
       <c r="AI384" t="inlineStr">
         <is>
+          <t>42072 CAROLINA FREYRE ARIAS/42072 CAROLINA FREYRE ARIAS</t>
+        </is>
+      </c>
+      <c r="AJ384" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK384" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -59054,6 +62894,16 @@
         </is>
       </c>
       <c r="AI385" t="inlineStr">
+        <is>
+          <t>PNP ALFEREZ MARIANO SANTOS MATEOS/PNP ALFEREZ MARIANO SANTOS MATEOS</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -59212,6 +63062,16 @@
       </c>
       <c r="AI386" t="inlineStr">
         <is>
+          <t>42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -59369,6 +63229,16 @@
       </c>
       <c r="AI387" t="inlineStr">
         <is>
+          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
+        </is>
+      </c>
+      <c r="AJ387" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK387" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -59516,6 +63386,16 @@
       </c>
       <c r="AI388" t="inlineStr">
         <is>
+          <t>CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AJ388" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK388" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -59672,6 +63552,16 @@
         </is>
       </c>
       <c r="AI389" t="inlineStr">
+        <is>
+          <t>FRANCISCO ANTONIO DE ZELA/FRANCISCO ANTONIO DE ZELA/FRANCISCO ANTONIO DE ZELA</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -59828,6 +63718,16 @@
       </c>
       <c r="AI390" t="inlineStr">
         <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AJ390" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK390" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -59983,6 +63883,16 @@
       </c>
       <c r="AI391" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AJ391" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK391" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60138,6 +64048,16 @@
       </c>
       <c r="AI392" t="inlineStr">
         <is>
+          <t>42106 MANUEL A. ODRIA/42106 MANUEL A. ODRIA</t>
+        </is>
+      </c>
+      <c r="AJ392" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK392" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60293,6 +64213,16 @@
       </c>
       <c r="AI393" t="inlineStr">
         <is>
+          <t>42231/42231/42231</t>
+        </is>
+      </c>
+      <c r="AJ393" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK393" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60448,6 +64378,16 @@
       </c>
       <c r="AI394" t="inlineStr">
         <is>
+          <t>42212</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60603,6 +64543,16 @@
       </c>
       <c r="AI395" t="inlineStr">
         <is>
+          <t>42105 RAMON CASTILLA/42105 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="AJ395" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK395" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60758,6 +64708,16 @@
       </c>
       <c r="AI396" t="inlineStr">
         <is>
+          <t>42103 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -60913,6 +64873,16 @@
       </c>
       <c r="AI397" t="inlineStr">
         <is>
+          <t>42104</t>
+        </is>
+      </c>
+      <c r="AJ397" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK397" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -61068,6 +65038,16 @@
       </c>
       <c r="AI398" t="inlineStr">
         <is>
+          <t>43010 HORACIO ZEBALLOS GAMEZ/43010 HORACIO ZEBALLOS GAMEZ/43010 HORACIO ZEBALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="AJ398" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK398" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -61223,6 +65203,16 @@
       </c>
       <c r="AI399" t="inlineStr">
         <is>
+          <t>42232 MODESTO BASADRE</t>
+        </is>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -61377,6 +65367,16 @@
         </is>
       </c>
       <c r="AI400" t="inlineStr">
+        <is>
+          <t>42234 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AJ400" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK400" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
@@ -61502,6 +65502,16 @@
         </is>
       </c>
       <c r="AI401" t="inlineStr">
+        <is>
+          <t>64109 GLISERIO PIMENTEL ESPINOZA</t>
+        </is>
+      </c>
+      <c r="AJ401" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK401" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Ucayali</t>
         </is>
@@ -61620,6 +65630,16 @@
       </c>
       <c r="AI402" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Ucayali</t>
         </is>
       </c>
@@ -61791,6 +65811,16 @@
       </c>
       <c r="AI403" t="inlineStr">
         <is>
+          <t>AGROP. LEONCIO PRADO/64962</t>
+        </is>
+      </c>
+      <c r="AJ403" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AK403" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sepahua</t>
         </is>
       </c>
@@ -61962,6 +65992,16 @@
       </c>
       <c r="AI404" t="inlineStr">
         <is>
+          <t>65292-B</t>
+        </is>
+      </c>
+      <c r="AJ404" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK404" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sepahua</t>
         </is>
       </c>
@@ -62132,6 +66172,16 @@
         </is>
       </c>
       <c r="AI405" t="inlineStr">
+        <is>
+          <t>65388</t>
+        </is>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AK405" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Sepahua</t>
         </is>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_anexo2_c.xlsx
@@ -419,152 +419,152 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Provincia</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nombre de la I.E.</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>¿Recibió mantenimiento preventivo? (SÍ / NO)</t>
+          <t>recibio_mantenimiento_preventivo_si_no</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Fecha de inicio de actividades de mantenimiento preventivo (o estimada)</t>
+          <t>fecha_de_inicio_de_actividades_de_mantenimiento_preventivo_o</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Fecha de culminación de actividades de mantenimiento preventivo (o estimada)</t>
+          <t>fecha_de_culminacion_de_actividades_de_mantenimiento_prevent</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Monto incurrido en el mantenimiento preventivo (S/)</t>
+          <t>monto_incurrido_en_el_mantenimiento_preventivo_s</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>¿Recibió mantenimiento correctivo? (SÍ / NO)</t>
+          <t>recibio_mantenimiento_correctivo_si_no</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Fecha de inicio de actividades de mantenimiento correctivo (o estimada)</t>
+          <t>fecha_de_inicio_de_actividades_de_mantenimiento_correctivo_o</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Fecha de culminación de actividades de mantenimiento correctivo (o estimada)</t>
+          <t>fecha_de_culminacion_de_actividades_de_mantenimiento_correct</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Monto incurrido en el mantenimiento correctivo (S/)</t>
+          <t>monto_incurrido_en_el_mantenimiento_correctivo_s</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en cercos perimétricos? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_cercos_perimetricos_s</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en tanques elevados? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_tanques_elevados_si_n</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en cisternas de agua y equipos de bombeo? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_cisternas_de_agua_y_e</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en instalación y/o rehabilitación de iNOdoros lavaderos urinarios y caños de lavaderos? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_instalacion_y_o_rehab</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en bebederos? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_bebederos_si_no</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en la sustitución y/o instalación de canaletas aéreas y drenaje pluvial? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_la_sustitucion_y_o_in</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en instalaciones de conexiones salidas y conductores eléctricos? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_instalaciones_de_cone</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en canalización y cajas de instalaciones eléctricas? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_canalizacion_y_cajas</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en tableros o gabinetes eléctricos? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_tableros_o_gabinetes</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en sistemas de puesta a tierra? (SÍ / NO)</t>
+          <t>la_intervencion_implico_actividades_en_sistemas_de_puesta_a</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>¿La intervención resolvió la necesidad del local educativo? (Es decir luego del mantenimiento correctivo y/o preventivo NO se requiere intervención adicional en los componentes NO estructurales de la infraestructura) (SÍ / NO)</t>
+          <t>la_intervencion_resolvio_la_necesidad_del_local_educativo_es</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>REMITENTE</t>
+          <t>remitente</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
